--- a/docs/workbook-split/dateien/Stunden.xlsx
+++ b/docs/workbook-split/dateien/Stunden.xlsx
@@ -673,45 +673,35 @@
       <c r="C7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,1)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$E$7:$E$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,1),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C7)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$B$1142:$B$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C7)))</f>
-        <v/>
-      </c>
-      <c r="E7" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,1)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$F$7:$F$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,1),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C7)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$C$1142:$C$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C7)))</f>
-        <v/>
-      </c>
-      <c r="F7" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,1)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$G$7:$G$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,1),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C7)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$D$1142:$D$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C7)))</f>
-        <v/>
-      </c>
-      <c r="G7" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,1)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$H$7:$H$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,1),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C7)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$E$1142:$E$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C7)))</f>
-        <v/>
-      </c>
-      <c r="H7" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,1)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$I$7:$I$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,1),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C7)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$F$1142:$F$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C7)))</f>
-        <v/>
-      </c>
-      <c r="I7" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,1)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$J$7:$J$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,1),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C7)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$G$1142:$G$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C7)))</f>
-        <v/>
-      </c>
-      <c r="J7" s="7">
-        <f>IF(ISNUMBER(D7),IF(SUM(D7:E7)=0,"n.a.",D7/SUM(D7:E7)),"")</f>
-        <v/>
-      </c>
-      <c r="K7" s="7">
-        <f>IF(ISNUMBER(I7),IF(I7=0,"n.a.",D7/I7),"")</f>
-        <v/>
-      </c>
-      <c r="L7" s="1">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C7)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$M$1142:$M$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C7))</f>
-        <v/>
-      </c>
-      <c r="M7" s="6">
-        <f>IF(ISNUMBER(I7),I7-SUM(D7:H7),"")</f>
-        <v/>
+      <c r="D7" s="6" t="n">
+        <v>4837.75</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>228</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>593</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>440</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>6758.75</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>0.9549918570794058</v>
+      </c>
+      <c r="K7" s="7" t="n">
+        <v>0.715775846125393</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>360</v>
       </c>
       <c r="N7" s="1" t="n"/>
       <c r="O7" s="1" t="n"/>
@@ -722,45 +712,35 @@
       <c r="C8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,2)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$E$7:$E$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,2),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C8)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$B$1142:$B$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C8)))</f>
-        <v/>
-      </c>
-      <c r="E8" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,2)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$F$7:$F$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,2),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C8)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$C$1142:$C$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C8)))</f>
-        <v/>
-      </c>
-      <c r="F8" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,2)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$G$7:$G$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,2),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C8)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$D$1142:$D$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C8)))</f>
-        <v/>
-      </c>
-      <c r="G8" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,2)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$H$7:$H$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,2),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C8)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$E$1142:$E$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C8)))</f>
-        <v/>
-      </c>
-      <c r="H8" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,2)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$I$7:$I$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,2),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C8)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$F$1142:$F$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C8)))</f>
-        <v/>
-      </c>
-      <c r="I8" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,2)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$J$7:$J$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,2),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C8)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$G$1142:$G$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C8)))</f>
-        <v/>
-      </c>
-      <c r="J8" s="7">
-        <f>IF(ISNUMBER(D8),IF(SUM(D8:E8)=0,"n.a.",D8/SUM(D8:E8)),"")</f>
-        <v/>
-      </c>
-      <c r="K8" s="7">
-        <f>IF(ISNUMBER(I8),IF(I8=0,"n.a.",D8/I8),"")</f>
-        <v/>
-      </c>
-      <c r="L8" s="1">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C8)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$M$1142:$M$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C8))</f>
-        <v/>
-      </c>
-      <c r="M8" s="6">
-        <f>IF(ISNUMBER(I8),I8-SUM(D8:H8),"")</f>
-        <v/>
+      <c r="D8" s="6" t="n">
+        <v>4853.5</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>317</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>494.5</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>528</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>6291</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>0.9386906488734165</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>0.7714989667779367</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="M8" s="6" t="n">
+        <v>98</v>
       </c>
       <c r="N8" s="1" t="n"/>
       <c r="O8" s="1" t="n"/>
@@ -771,45 +751,35 @@
       <c r="C9" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,3)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$E$7:$E$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,3),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C9)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$B$1142:$B$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C9)))</f>
-        <v/>
-      </c>
-      <c r="E9" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,3)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$F$7:$F$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,3),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C9)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$C$1142:$C$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C9)))</f>
-        <v/>
-      </c>
-      <c r="F9" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,3)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$G$7:$G$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,3),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C9)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$D$1142:$D$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C9)))</f>
-        <v/>
-      </c>
-      <c r="G9" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,3)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$H$7:$H$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,3),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C9)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$E$1142:$E$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C9)))</f>
-        <v/>
-      </c>
-      <c r="H9" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,3)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$I$7:$I$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,3),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C9)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$F$1142:$F$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C9)))</f>
-        <v/>
-      </c>
-      <c r="I9" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,3)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$J$7:$J$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,3),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C9)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$G$1142:$G$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C9)))</f>
-        <v/>
-      </c>
-      <c r="J9" s="7">
-        <f>IF(ISNUMBER(D9),IF(SUM(D9:E9)=0,"n.a.",D9/SUM(D9:E9)),"")</f>
-        <v/>
-      </c>
-      <c r="K9" s="7">
-        <f>IF(ISNUMBER(I9),IF(I9=0,"n.a.",D9/I9),"")</f>
-        <v/>
-      </c>
-      <c r="L9" s="1">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C9)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$M$1142:$M$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C9))</f>
-        <v/>
-      </c>
-      <c r="M9" s="6">
-        <f>IF(ISNUMBER(I9),I9-SUM(D9:H9),"")</f>
-        <v/>
+      <c r="D9" s="6" t="n">
+        <v>6095</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>290</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>640</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>447</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>7632</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>0.9545810493343775</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <v>0.7986111111111112</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>160</v>
       </c>
       <c r="N9" s="1" t="n"/>
       <c r="O9" s="1" t="n"/>
@@ -820,45 +790,35 @@
       <c r="C10" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,4)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$E$7:$E$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,4),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C10)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$B$1142:$B$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C10)))</f>
-        <v/>
-      </c>
-      <c r="E10" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,4)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$F$7:$F$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,4),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C10)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$C$1142:$C$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C10)))</f>
-        <v/>
-      </c>
-      <c r="F10" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,4)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$G$7:$G$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,4),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C10)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$D$1142:$D$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C10)))</f>
-        <v/>
-      </c>
-      <c r="G10" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,4)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$H$7:$H$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,4),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C10)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$E$1142:$E$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C10)))</f>
-        <v/>
-      </c>
-      <c r="H10" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,4)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$I$7:$I$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,4),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C10)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$F$1142:$F$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C10)))</f>
-        <v/>
-      </c>
-      <c r="I10" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,4)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$J$7:$J$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,4),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C10)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$G$1142:$G$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C10)))</f>
-        <v/>
-      </c>
-      <c r="J10" s="7">
-        <f>IF(ISNUMBER(D10),IF(SUM(D10:E10)=0,"n.a.",D10/SUM(D10:E10)),"")</f>
-        <v/>
-      </c>
-      <c r="K10" s="7">
-        <f>IF(ISNUMBER(I10),IF(I10=0,"n.a.",D10/I10),"")</f>
-        <v/>
-      </c>
-      <c r="L10" s="1">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C10)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$M$1142:$M$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C10))</f>
-        <v/>
-      </c>
-      <c r="M10" s="6">
-        <f>IF(ISNUMBER(I10),I10-SUM(D10:H10),"")</f>
-        <v/>
+      <c r="D10" s="6" t="n">
+        <v>4640.75</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>376.5</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>721</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>648</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>670</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>7305.25</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>0.9249588918232099</v>
+      </c>
+      <c r="K10" s="7" t="n">
+        <v>0.6352623113514253</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="M10" s="6" t="n">
+        <v>249</v>
       </c>
       <c r="N10" s="1" t="n"/>
       <c r="O10" s="1" t="n"/>
@@ -869,45 +829,35 @@
       <c r="C11" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D11" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,5)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$E$7:$E$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,5),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C11)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$B$1142:$B$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C11)))</f>
-        <v/>
-      </c>
-      <c r="E11" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,5)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$F$7:$F$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,5),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C11)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$C$1142:$C$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C11)))</f>
-        <v/>
-      </c>
-      <c r="F11" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,5)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$G$7:$G$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,5),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C11)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$D$1142:$D$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C11)))</f>
-        <v/>
-      </c>
-      <c r="G11" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,5)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$H$7:$H$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,5),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C11)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$E$1142:$E$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C11)))</f>
-        <v/>
-      </c>
-      <c r="H11" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,5)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$I$7:$I$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,5),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C11)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$F$1142:$F$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C11)))</f>
-        <v/>
-      </c>
-      <c r="I11" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,5)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$J$7:$J$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,5),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C11)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$G$1142:$G$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C11)))</f>
-        <v/>
-      </c>
-      <c r="J11" s="7">
-        <f>IF(ISNUMBER(D11),IF(SUM(D11:E11)=0,"n.a.",D11/SUM(D11:E11)),"")</f>
-        <v/>
-      </c>
-      <c r="K11" s="7">
-        <f>IF(ISNUMBER(I11),IF(I11=0,"n.a.",D11/I11),"")</f>
-        <v/>
-      </c>
-      <c r="L11" s="1">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C11)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$M$1142:$M$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C11))</f>
-        <v/>
-      </c>
-      <c r="M11" s="6">
-        <f>IF(ISNUMBER(I11),I11-SUM(D11:H11),"")</f>
-        <v/>
+      <c r="D11" s="6" t="n">
+        <v>3938.75</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>446.5</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>610.5</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>501</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>997</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>6704.75</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>0.8981814035687817</v>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>0.5874566538647974</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>211</v>
       </c>
       <c r="N11" s="1" t="n"/>
       <c r="O11" s="1" t="n"/>
@@ -918,46 +868,16 @@
       <c r="C12" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D12" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,6)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$E$7:$E$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,6),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C12)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$B$1142:$B$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C12)))</f>
-        <v/>
-      </c>
-      <c r="E12" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,6)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$F$7:$F$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,6),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C12)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$C$1142:$C$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C12)))</f>
-        <v/>
-      </c>
-      <c r="F12" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,6)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$G$7:$G$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,6),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C12)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$D$1142:$D$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C12)))</f>
-        <v/>
-      </c>
-      <c r="G12" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,6)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$H$7:$H$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,6),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C12)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$E$1142:$E$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C12)))</f>
-        <v/>
-      </c>
-      <c r="H12" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,6)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$I$7:$I$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,6),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C12)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$F$1142:$F$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C12)))</f>
-        <v/>
-      </c>
-      <c r="I12" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,6)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$J$7:$J$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,6),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C12)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$G$1142:$G$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C12)))</f>
-        <v/>
-      </c>
-      <c r="J12" s="7">
-        <f>IF(ISNUMBER(D12),IF(SUM(D12:E12)=0,"n.a.",D12/SUM(D12:E12)),"")</f>
-        <v/>
-      </c>
-      <c r="K12" s="7">
-        <f>IF(ISNUMBER(I12),IF(I12=0,"n.a.",D12/I12),"")</f>
-        <v/>
-      </c>
-      <c r="L12" s="1">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C12)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$M$1142:$M$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C12))</f>
-        <v/>
-      </c>
-      <c r="M12" s="6">
-        <f>IF(ISNUMBER(I12),I12-SUM(D12:H12),"")</f>
-        <v/>
-      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n"/>
+      <c r="J12" s="7" t="n"/>
+      <c r="K12" s="7" t="n"/>
+      <c r="L12" s="1" t="n"/>
+      <c r="M12" s="6" t="n"/>
       <c r="N12" s="1" t="n"/>
       <c r="O12" s="1" t="n"/>
     </row>
@@ -967,46 +887,16 @@
       <c r="C13" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D13" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,7)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$E$7:$E$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,7),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C13)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$B$1142:$B$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C13)))</f>
-        <v/>
-      </c>
-      <c r="E13" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,7)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$F$7:$F$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,7),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C13)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$C$1142:$C$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C13)))</f>
-        <v/>
-      </c>
-      <c r="F13" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,7)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$G$7:$G$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,7),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C13)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$D$1142:$D$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C13)))</f>
-        <v/>
-      </c>
-      <c r="G13" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,7)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$H$7:$H$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,7),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C13)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$E$1142:$E$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C13)))</f>
-        <v/>
-      </c>
-      <c r="H13" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,7)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$I$7:$I$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,7),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C13)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$F$1142:$F$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C13)))</f>
-        <v/>
-      </c>
-      <c r="I13" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,7)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$J$7:$J$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,7),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C13)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$G$1142:$G$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C13)))</f>
-        <v/>
-      </c>
-      <c r="J13" s="7">
-        <f>IF(ISNUMBER(D13),IF(SUM(D13:E13)=0,"n.a.",D13/SUM(D13:E13)),"")</f>
-        <v/>
-      </c>
-      <c r="K13" s="7">
-        <f>IF(ISNUMBER(I13),IF(I13=0,"n.a.",D13/I13),"")</f>
-        <v/>
-      </c>
-      <c r="L13" s="1">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C13)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$M$1142:$M$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C13))</f>
-        <v/>
-      </c>
-      <c r="M13" s="6">
-        <f>IF(ISNUMBER(I13),I13-SUM(D13:H13),"")</f>
-        <v/>
-      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n"/>
+      <c r="J13" s="7" t="n"/>
+      <c r="K13" s="7" t="n"/>
+      <c r="L13" s="1" t="n"/>
+      <c r="M13" s="6" t="n"/>
       <c r="N13" s="1" t="n"/>
       <c r="O13" s="1" t="n"/>
     </row>
@@ -1016,46 +906,16 @@
       <c r="C14" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="D14" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,8)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$E$7:$E$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,8),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C14)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$B$1142:$B$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C14)))</f>
-        <v/>
-      </c>
-      <c r="E14" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,8)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$F$7:$F$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,8),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C14)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$C$1142:$C$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C14)))</f>
-        <v/>
-      </c>
-      <c r="F14" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,8)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$G$7:$G$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,8),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C14)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$D$1142:$D$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C14)))</f>
-        <v/>
-      </c>
-      <c r="G14" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,8)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$H$7:$H$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,8),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C14)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$E$1142:$E$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C14)))</f>
-        <v/>
-      </c>
-      <c r="H14" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,8)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$I$7:$I$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,8),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C14)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$F$1142:$F$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C14)))</f>
-        <v/>
-      </c>
-      <c r="I14" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,8)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$J$7:$J$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,8),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C14)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$G$1142:$G$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C14)))</f>
-        <v/>
-      </c>
-      <c r="J14" s="7">
-        <f>IF(ISNUMBER(D14),IF(SUM(D14:E14)=0,"n.a.",D14/SUM(D14:E14)),"")</f>
-        <v/>
-      </c>
-      <c r="K14" s="7">
-        <f>IF(ISNUMBER(I14),IF(I14=0,"n.a.",D14/I14),"")</f>
-        <v/>
-      </c>
-      <c r="L14" s="1">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C14)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$M$1142:$M$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C14))</f>
-        <v/>
-      </c>
-      <c r="M14" s="6">
-        <f>IF(ISNUMBER(I14),I14-SUM(D14:H14),"")</f>
-        <v/>
-      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="7" t="n"/>
+      <c r="K14" s="7" t="n"/>
+      <c r="L14" s="1" t="n"/>
+      <c r="M14" s="6" t="n"/>
       <c r="N14" s="1" t="n"/>
       <c r="O14" s="1" t="n"/>
     </row>
@@ -1065,46 +925,16 @@
       <c r="C15" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="D15" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,9)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$E$7:$E$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,9),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C15)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$B$1142:$B$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C15)))</f>
-        <v/>
-      </c>
-      <c r="E15" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,9)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$F$7:$F$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,9),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C15)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$C$1142:$C$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C15)))</f>
-        <v/>
-      </c>
-      <c r="F15" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,9)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$G$7:$G$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,9),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C15)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$D$1142:$D$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C15)))</f>
-        <v/>
-      </c>
-      <c r="G15" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,9)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$H$7:$H$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,9),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C15)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$E$1142:$E$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C15)))</f>
-        <v/>
-      </c>
-      <c r="H15" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,9)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$I$7:$I$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,9),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C15)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$F$1142:$F$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C15)))</f>
-        <v/>
-      </c>
-      <c r="I15" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,9)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$J$7:$J$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,9),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C15)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$G$1142:$G$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C15)))</f>
-        <v/>
-      </c>
-      <c r="J15" s="7">
-        <f>IF(ISNUMBER(D15),IF(SUM(D15:E15)=0,"n.a.",D15/SUM(D15:E15)),"")</f>
-        <v/>
-      </c>
-      <c r="K15" s="7">
-        <f>IF(ISNUMBER(I15),IF(I15=0,"n.a.",D15/I15),"")</f>
-        <v/>
-      </c>
-      <c r="L15" s="1">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C15)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$M$1142:$M$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C15))</f>
-        <v/>
-      </c>
-      <c r="M15" s="6">
-        <f>IF(ISNUMBER(I15),I15-SUM(D15:H15),"")</f>
-        <v/>
-      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="7" t="n"/>
+      <c r="K15" s="7" t="n"/>
+      <c r="L15" s="1" t="n"/>
+      <c r="M15" s="6" t="n"/>
       <c r="N15" s="1" t="n"/>
       <c r="O15" s="1" t="n"/>
     </row>
@@ -1114,46 +944,16 @@
       <c r="C16" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="D16" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,10)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$E$7:$E$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,10),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C16)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$B$1142:$B$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C16)))</f>
-        <v/>
-      </c>
-      <c r="E16" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,10)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$F$7:$F$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,10),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C16)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$C$1142:$C$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C16)))</f>
-        <v/>
-      </c>
-      <c r="F16" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,10)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$G$7:$G$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,10),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C16)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$D$1142:$D$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C16)))</f>
-        <v/>
-      </c>
-      <c r="G16" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,10)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$H$7:$H$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,10),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C16)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$E$1142:$E$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C16)))</f>
-        <v/>
-      </c>
-      <c r="H16" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,10)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$I$7:$I$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,10),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C16)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$F$1142:$F$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C16)))</f>
-        <v/>
-      </c>
-      <c r="I16" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,10)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$J$7:$J$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,10),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C16)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$G$1142:$G$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C16)))</f>
-        <v/>
-      </c>
-      <c r="J16" s="7">
-        <f>IF(ISNUMBER(D16),IF(SUM(D16:E16)=0,"n.a.",D16/SUM(D16:E16)),"")</f>
-        <v/>
-      </c>
-      <c r="K16" s="7">
-        <f>IF(ISNUMBER(I16),IF(I16=0,"n.a.",D16/I16),"")</f>
-        <v/>
-      </c>
-      <c r="L16" s="1">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C16)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$M$1142:$M$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C16))</f>
-        <v/>
-      </c>
-      <c r="M16" s="6">
-        <f>IF(ISNUMBER(I16),I16-SUM(D16:H16),"")</f>
-        <v/>
-      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n"/>
+      <c r="J16" s="7" t="n"/>
+      <c r="K16" s="7" t="n"/>
+      <c r="L16" s="1" t="n"/>
+      <c r="M16" s="6" t="n"/>
       <c r="N16" s="1" t="n"/>
       <c r="O16" s="1" t="n"/>
     </row>
@@ -1163,46 +963,16 @@
       <c r="C17" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D17" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,11)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$E$7:$E$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,11),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C17)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$B$1142:$B$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C17)))</f>
-        <v/>
-      </c>
-      <c r="E17" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,11)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$F$7:$F$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,11),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C17)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$C$1142:$C$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C17)))</f>
-        <v/>
-      </c>
-      <c r="F17" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,11)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$G$7:$G$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,11),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C17)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$D$1142:$D$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C17)))</f>
-        <v/>
-      </c>
-      <c r="G17" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,11)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$H$7:$H$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,11),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C17)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$E$1142:$E$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C17)))</f>
-        <v/>
-      </c>
-      <c r="H17" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,11)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$I$7:$I$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,11),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C17)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$F$1142:$F$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C17)))</f>
-        <v/>
-      </c>
-      <c r="I17" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,11)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$J$7:$J$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,11),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C17)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$G$1142:$G$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C17)))</f>
-        <v/>
-      </c>
-      <c r="J17" s="7">
-        <f>IF(ISNUMBER(D17),IF(SUM(D17:E17)=0,"n.a.",D17/SUM(D17:E17)),"")</f>
-        <v/>
-      </c>
-      <c r="K17" s="7">
-        <f>IF(ISNUMBER(I17),IF(I17=0,"n.a.",D17/I17),"")</f>
-        <v/>
-      </c>
-      <c r="L17" s="1">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C17)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$M$1142:$M$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C17))</f>
-        <v/>
-      </c>
-      <c r="M17" s="6">
-        <f>IF(ISNUMBER(I17),I17-SUM(D17:H17),"")</f>
-        <v/>
-      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="7" t="n"/>
+      <c r="K17" s="7" t="n"/>
+      <c r="L17" s="1" t="n"/>
+      <c r="M17" s="6" t="n"/>
       <c r="N17" s="1" t="n"/>
       <c r="O17" s="1" t="n"/>
     </row>
@@ -1212,46 +982,16 @@
       <c r="C18" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D18" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,12)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$E$7:$E$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,12),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C18)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$B$1142:$B$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C18)))</f>
-        <v/>
-      </c>
-      <c r="E18" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,12)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$F$7:$F$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,12),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C18)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$C$1142:$C$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C18)))</f>
-        <v/>
-      </c>
-      <c r="F18" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,12)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$G$7:$G$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,12),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C18)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$D$1142:$D$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C18)))</f>
-        <v/>
-      </c>
-      <c r="G18" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,12)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$H$7:$H$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,12),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C18)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$E$1142:$E$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C18)))</f>
-        <v/>
-      </c>
-      <c r="H18" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,12)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$I$7:$I$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,12),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C18)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$F$1142:$F$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C18)))</f>
-        <v/>
-      </c>
-      <c r="I18" s="6">
-        <f>IF(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,12)&gt;0,SUMIFS('[Import Stunden.xlsx]Import Stunden'!$J$7:$J$8,'[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,12),IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C18)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$G$1142:$G$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C18)))</f>
-        <v/>
-      </c>
-      <c r="J18" s="7">
-        <f>IF(ISNUMBER(D18),IF(SUM(D18:E18)=0,"n.a.",D18/SUM(D18:E18)),"")</f>
-        <v/>
-      </c>
-      <c r="K18" s="7">
-        <f>IF(ISNUMBER(I18),IF(I18=0,"n.a.",D18/I18),"")</f>
-        <v/>
-      </c>
-      <c r="L18" s="1">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C18)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$M$1142:$M$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,C18))</f>
-        <v/>
-      </c>
-      <c r="M18" s="6">
-        <f>IF(ISNUMBER(I18),I18-SUM(D18:H18),"")</f>
-        <v/>
-      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="7" t="n"/>
+      <c r="K18" s="7" t="n"/>
+      <c r="L18" s="1" t="n"/>
+      <c r="M18" s="6" t="n"/>
       <c r="N18" s="1" t="n"/>
       <c r="O18" s="1" t="n"/>
     </row>
@@ -1280,42 +1020,33 @@
           <t>Verfügbare Monate</t>
         </is>
       </c>
-      <c r="D20" s="9">
-        <f>SUM(D7:D18)</f>
-        <v/>
-      </c>
-      <c r="E20" s="9">
-        <f>SUM(E7:E18)</f>
-        <v/>
-      </c>
-      <c r="F20" s="9">
-        <f>SUM(F7:F18)</f>
-        <v/>
-      </c>
-      <c r="G20" s="9">
-        <f>SUM(G7:G18)</f>
-        <v/>
-      </c>
-      <c r="H20" s="9">
-        <f>SUM(H7:H18)</f>
-        <v/>
-      </c>
-      <c r="I20" s="9">
-        <f>SUM(I7:I18)</f>
-        <v/>
-      </c>
-      <c r="J20" s="10">
-        <f>D20/SUM(D20:E20)</f>
-        <v/>
-      </c>
-      <c r="K20" s="10">
-        <f>D20/I20</f>
-        <v/>
+      <c r="D20" s="9" t="n">
+        <v>24365.75</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>1658</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>3059</v>
+      </c>
+      <c r="G20" s="9" t="n">
+        <v>2564</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>1967</v>
+      </c>
+      <c r="I20" s="9" t="n">
+        <v>34691.75</v>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>0.9362889668091647</v>
+      </c>
+      <c r="K20" s="10" t="n">
+        <v>0.7023499823445055</v>
       </c>
       <c r="L20" s="8" t="n"/>
-      <c r="M20" s="6">
-        <f>SUM(M7:M18)</f>
-        <v/>
+      <c r="M20" s="6" t="n">
+        <v>1078</v>
       </c>
       <c r="N20" s="1" t="n"/>
       <c r="O20" s="1" t="n"/>
@@ -1777,13 +1508,11 @@
           <t>produktiv</t>
         </is>
       </c>
-      <c r="D47" s="6">
-        <f>'[D KLR.xlsx]D KLR'!B74</f>
-        <v/>
-      </c>
-      <c r="E47" s="7">
-        <f>D47/$D$53</f>
-        <v/>
+      <c r="D47" s="6" t="n">
+        <v>43294</v>
+      </c>
+      <c r="E47" s="7" t="n">
+        <v>0.670912753757942</v>
       </c>
       <c r="F47" s="1" t="n"/>
       <c r="G47" s="1" t="n"/>
@@ -1804,13 +1533,11 @@
           <t>unproduktiv</t>
         </is>
       </c>
-      <c r="D48" s="6">
-        <f>'[D KLR.xlsx]D KLR'!C74</f>
-        <v/>
-      </c>
-      <c r="E48" s="7">
-        <f>D48/$D$53</f>
-        <v/>
+      <c r="D48" s="6" t="n">
+        <v>5284.5</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>0.08189214318921433</v>
       </c>
       <c r="F48" s="1" t="n"/>
       <c r="G48" s="1" t="n"/>
@@ -1831,13 +1558,11 @@
           <t>urlaub</t>
         </is>
       </c>
-      <c r="D49" s="6">
-        <f>'[D KLR.xlsx]D KLR'!D74</f>
-        <v/>
-      </c>
-      <c r="E49" s="7">
-        <f>D49/$D$53</f>
-        <v/>
+      <c r="D49" s="6" t="n">
+        <v>6475</v>
+      </c>
+      <c r="E49" s="7" t="n">
+        <v>0.1003409267007593</v>
       </c>
       <c r="F49" s="1" t="n"/>
       <c r="G49" s="1" t="n"/>
@@ -1858,13 +1583,11 @@
           <t>krankheit</t>
         </is>
       </c>
-      <c r="D50" s="6">
-        <f>'[D KLR.xlsx]D KLR'!E74</f>
-        <v/>
-      </c>
-      <c r="E50" s="7">
-        <f>D50/$D$53</f>
-        <v/>
+      <c r="D50" s="6" t="n">
+        <v>5359.5</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>0.08305439330543933</v>
       </c>
       <c r="F50" s="1" t="n"/>
       <c r="G50" s="1" t="n"/>
@@ -1885,13 +1608,11 @@
           <t>feiertag</t>
         </is>
       </c>
-      <c r="D51" s="6">
-        <f>'[D KLR.xlsx]D KLR'!F74</f>
-        <v/>
-      </c>
-      <c r="E51" s="7">
-        <f>D51/$D$53</f>
-        <v/>
+      <c r="D51" s="6" t="n">
+        <v>2135</v>
+      </c>
+      <c r="E51" s="7" t="n">
+        <v>0.03308538664187199</v>
       </c>
       <c r="F51" s="1" t="n"/>
       <c r="G51" s="1" t="n"/>
@@ -1912,9 +1633,8 @@
           <t>Nicht aufgegliedert</t>
         </is>
       </c>
-      <c r="D52" s="6">
-        <f>D53-SUM(D47:D51)</f>
-        <v/>
+      <c r="D52" s="6" t="n">
+        <v>1982</v>
       </c>
       <c r="E52" s="1" t="n"/>
       <c r="F52" s="1" t="n"/>
@@ -1936,9 +1656,8 @@
           <t>Gesamt</t>
         </is>
       </c>
-      <c r="D53" s="9">
-        <f>'[D KLR.xlsx]D KLR'!G74</f>
-        <v/>
+      <c r="D53" s="9" t="n">
+        <v>64530</v>
       </c>
       <c r="E53" s="8" t="n"/>
       <c r="F53" s="1" t="n"/>
@@ -2071,6 +1790,8 @@
       <c r="N60" s="1" t="n"/>
       <c r="O60" s="1" t="n"/>
     </row>
+    <row r="61"/>
+    <row r="62"/>
     <row r="63">
       <c r="C63" t="inlineStr">
         <is>
